--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986859</v>
+        <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>88908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517919</v>
+        <v>517923</v>
       </c>
       <c r="R15" t="n">
-        <v>6982719</v>
+        <v>6982402</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,11 +2057,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986873</v>
+        <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>88908</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517923</v>
+        <v>517919</v>
       </c>
       <c r="R17" t="n">
-        <v>6982402</v>
+        <v>6982719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128986860</v>
       </c>
       <c r="B10" t="n">
-        <v>79210</v>
+        <v>79115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R11" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>91513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R12" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1782,7 @@
         <v>128986867</v>
       </c>
       <c r="B13" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>88908</v>
+        <v>88913</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>91809</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>91804</v>
+        <v>80134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R19" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>128986864</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B18" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R18" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>91805</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R19" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R4" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986854</v>
+        <v>128986856</v>
       </c>
       <c r="B5" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518021</v>
+        <v>517896</v>
       </c>
       <c r="R5" t="n">
-        <v>6982497</v>
+        <v>6982517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,46 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R7" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1245,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,34 +1283,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R8" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986874</v>
+        <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>92191</v>
+        <v>88923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517913</v>
+        <v>517923</v>
       </c>
       <c r="R15" t="n">
-        <v>6982711</v>
+        <v>6982402</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B17" t="n">
-        <v>88920</v>
+        <v>92196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R17" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>91808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>91805</v>
+        <v>80139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R19" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R4" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986854</v>
+        <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518021</v>
+        <v>517896</v>
       </c>
       <c r="R6" t="n">
-        <v>6982497</v>
+        <v>6982517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128986860</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>88923</v>
+        <v>88926</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986859</v>
+        <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>92199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517919</v>
+        <v>517913</v>
       </c>
       <c r="R16" t="n">
-        <v>6982719</v>
+        <v>6982711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2154,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2180,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986874</v>
+        <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>92196</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517913</v>
+        <v>517919</v>
       </c>
       <c r="R17" t="n">
-        <v>6982711</v>
+        <v>6982719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2285,7 +2285,7 @@
         <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128986864</v>
       </c>
       <c r="B20" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R6" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128986860</v>
       </c>
       <c r="B10" t="n">
-        <v>79121</v>
+        <v>79125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R11" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R12" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1782,7 @@
         <v>128986867</v>
       </c>
       <c r="B13" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B15" t="n">
-        <v>88926</v>
+        <v>92206</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R15" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986874</v>
+        <v>128986873</v>
       </c>
       <c r="B16" t="n">
-        <v>92199</v>
+        <v>88930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517913</v>
+        <v>517923</v>
       </c>
       <c r="R16" t="n">
-        <v>6982711</v>
+        <v>6982402</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>80144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R18" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>91818</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R19" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>128986864</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R4" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986856</v>
+        <v>128986854</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517896</v>
+        <v>518021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982517</v>
+        <v>6982497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R6" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1986,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986874</v>
+        <v>128986859</v>
       </c>
       <c r="B15" t="n">
-        <v>92206</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517913</v>
+        <v>517919</v>
       </c>
       <c r="R15" t="n">
-        <v>6982711</v>
+        <v>6982719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,6 +2057,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2088,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>88930</v>
+        <v>92206</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R16" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986859</v>
+        <v>128986873</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>88930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517919</v>
+        <v>517923</v>
       </c>
       <c r="R17" t="n">
-        <v>6982719</v>
+        <v>6982402</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R4" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986856</v>
+        <v>128986854</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517896</v>
+        <v>518021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982517</v>
+        <v>6982497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1181,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R7" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,7 +1257,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,46 +1295,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R8" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R11" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,11 +1651,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R12" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,6 +1748,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986859</v>
+        <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>88937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517919</v>
+        <v>517923</v>
       </c>
       <c r="R15" t="n">
-        <v>6982719</v>
+        <v>6982402</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,11 +2057,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,7 +2086,7 @@
         <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>92206</v>
+        <v>92213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986873</v>
+        <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>88930</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517923</v>
+        <v>517919</v>
       </c>
       <c r="R17" t="n">
-        <v>6982402</v>
+        <v>6982719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2251,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>80144</v>
+        <v>91825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>91818</v>
+        <v>80144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R19" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R4" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986854</v>
+        <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518021</v>
+        <v>517896</v>
       </c>
       <c r="R6" t="n">
-        <v>6982497</v>
+        <v>6982517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1144,6 +1139,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,7 +1173,7 @@
         <v>128986858</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>128986871</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>128986860</v>
       </c>
       <c r="B10" t="n">
-        <v>79125</v>
+        <v>79127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R11" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R12" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1782,7 @@
         <v>128986867</v>
       </c>
       <c r="B13" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128986864</v>
       </c>
       <c r="B20" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R4" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,46 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R7" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1245,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1295,34 +1283,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R8" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R11" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,11 +1651,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1688,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R12" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,6 +1748,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R4" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1389,7 +1389,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R11" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,6 +1651,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R12" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,11 +1753,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B15" t="n">
-        <v>88939</v>
+        <v>92230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R15" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986874</v>
+        <v>128986873</v>
       </c>
       <c r="B16" t="n">
-        <v>92215</v>
+        <v>88940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517913</v>
+        <v>517923</v>
       </c>
       <c r="R16" t="n">
-        <v>6982711</v>
+        <v>6982402</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2282,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B18" t="n">
-        <v>91827</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R18" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R19" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,14 +792,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -869,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +876,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R4" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +936,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1033,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1389,7 +1385,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1986,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986874</v>
+        <v>128986859</v>
       </c>
       <c r="B15" t="n">
-        <v>92230</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517913</v>
+        <v>517919</v>
       </c>
       <c r="R15" t="n">
-        <v>6982711</v>
+        <v>6982719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,6 +2053,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>88940</v>
+        <v>92231</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R16" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986859</v>
+        <v>128986873</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>88940</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2192,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517919</v>
+        <v>517923</v>
       </c>
       <c r="R17" t="n">
-        <v>6982719</v>
+        <v>6982402</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2251,11 +2252,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2378,7 @@
         <v>128986863</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R6" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R11" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,11 +1647,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1678,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1689,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R12" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1744,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986859</v>
+        <v>128986874</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>92231</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517919</v>
+        <v>517913</v>
       </c>
       <c r="R15" t="n">
-        <v>6982719</v>
+        <v>6982711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,11 +2053,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986874</v>
+        <v>128986873</v>
       </c>
       <c r="B16" t="n">
-        <v>92231</v>
+        <v>88940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517913</v>
+        <v>517923</v>
       </c>
       <c r="R16" t="n">
-        <v>6982711</v>
+        <v>6982402</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986873</v>
+        <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>88940</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2192,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517923</v>
+        <v>517919</v>
       </c>
       <c r="R17" t="n">
-        <v>6982402</v>
+        <v>6982719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,6 +2247,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R19" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986854</v>
+        <v>128986856</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,21 +876,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518021</v>
+        <v>517896</v>
       </c>
       <c r="R4" t="n">
-        <v>6982497</v>
+        <v>6982517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -936,6 +936,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986856</v>
+        <v>128986854</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517896</v>
+        <v>518021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982517</v>
+        <v>6982497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1033,11 +1038,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,7 +1067,7 @@
         <v>128986869</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,34 +1177,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R7" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,7 +1253,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,46 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R8" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1385,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128986860</v>
       </c>
       <c r="B10" t="n">
-        <v>79127</v>
+        <v>79129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>128986874</v>
       </c>
       <c r="B15" t="n">
-        <v>92231</v>
+        <v>92234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>128986873</v>
       </c>
       <c r="B16" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>128986864</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -865,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986856</v>
+        <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,21 +876,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517896</v>
+        <v>518021</v>
       </c>
       <c r="R4" t="n">
-        <v>6982517</v>
+        <v>6982497</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -936,11 +936,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1033,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R6" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986874</v>
+        <v>128986873</v>
       </c>
       <c r="B15" t="n">
-        <v>92234</v>
+        <v>88943</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517913</v>
+        <v>517923</v>
       </c>
       <c r="R15" t="n">
-        <v>6982711</v>
+        <v>6982402</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>88943</v>
+        <v>92234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R16" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R6" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,7 +1283,7 @@
         <v>128986871</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>128986860</v>
       </c>
       <c r="B10" t="n">
-        <v>79129</v>
+        <v>79130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986873</v>
+        <v>128986874</v>
       </c>
       <c r="B15" t="n">
-        <v>88943</v>
+        <v>92236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517923</v>
+        <v>517913</v>
       </c>
       <c r="R15" t="n">
-        <v>6982402</v>
+        <v>6982711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986874</v>
+        <v>128986859</v>
       </c>
       <c r="B16" t="n">
-        <v>92234</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517913</v>
+        <v>517919</v>
       </c>
       <c r="R16" t="n">
-        <v>6982711</v>
+        <v>6982719</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,6 +2150,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2176,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986859</v>
+        <v>128986873</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>88945</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2187,21 +2192,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2211,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517919</v>
+        <v>517923</v>
       </c>
       <c r="R17" t="n">
-        <v>6982719</v>
+        <v>6982402</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,11 +2252,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B18" t="n">
-        <v>91841</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R18" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B19" t="n">
-        <v>80148</v>
+        <v>91843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R19" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>128986864</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R6" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,46 +1177,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R7" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,7 +1241,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1279,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R8" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1385,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R11" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,6 +1647,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1689,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R12" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,11 +1749,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986874</v>
+        <v>128986859</v>
       </c>
       <c r="B15" t="n">
-        <v>92236</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517913</v>
+        <v>517919</v>
       </c>
       <c r="R15" t="n">
-        <v>6982711</v>
+        <v>6982719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,6 +2053,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2079,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986859</v>
+        <v>128986874</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>92240</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517919</v>
+        <v>517913</v>
       </c>
       <c r="R16" t="n">
-        <v>6982719</v>
+        <v>6982711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,11 +2155,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2184,7 +2184,7 @@
         <v>128986873</v>
       </c>
       <c r="B17" t="n">
-        <v>88945</v>
+        <v>88949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986865</v>
+        <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>91847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>517835</v>
+        <v>518023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982835</v>
+        <v>6982495</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986863</v>
+        <v>128986865</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2386,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2410,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518023</v>
+        <v>517835</v>
       </c>
       <c r="R19" t="n">
-        <v>6982495</v>
+        <v>6982835</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986861</v>
       </c>
       <c r="B2" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128986868</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986856</v>
+        <v>128986869</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517896</v>
+        <v>517784</v>
       </c>
       <c r="R6" t="n">
-        <v>6982517</v>
+        <v>6982724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,34 +1177,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R7" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,7 +1253,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,46 +1291,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R8" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,7 +1385,7 @@
         <v>128986862</v>
       </c>
       <c r="B9" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R11" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,11 +1647,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1678,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1689,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1713,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R12" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1749,6 +1744,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,32 +1982,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986859</v>
+        <v>128986874</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>92241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517919</v>
+        <v>517913</v>
       </c>
       <c r="R15" t="n">
-        <v>6982719</v>
+        <v>6982711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,11 +2053,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,32 +2079,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986874</v>
+        <v>128986873</v>
       </c>
       <c r="B16" t="n">
-        <v>92240</v>
+        <v>88950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2114,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517913</v>
+        <v>517923</v>
       </c>
       <c r="R16" t="n">
-        <v>6982711</v>
+        <v>6982402</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,10 +2176,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986873</v>
+        <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>88949</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2192,21 +2187,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2216,10 +2211,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517923</v>
+        <v>517919</v>
       </c>
       <c r="R17" t="n">
-        <v>6982402</v>
+        <v>6982719</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,6 +2247,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2281,7 +2281,7 @@
         <v>128986863</v>
       </c>
       <c r="B18" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -865,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,21 +876,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R4" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -936,6 +936,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,10 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986856</v>
+        <v>128986854</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517896</v>
+        <v>518021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982517</v>
+        <v>6982497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1033,11 +1038,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986869</v>
+        <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517784</v>
+        <v>517896</v>
       </c>
       <c r="R6" t="n">
-        <v>6982724</v>
+        <v>6982517</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1166,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986858</v>
+        <v>128986871</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,46 +1177,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518046</v>
+        <v>517990</v>
       </c>
       <c r="R7" t="n">
-        <v>6982481</v>
+        <v>6982404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,7 +1241,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986871</v>
+        <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1279,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517990</v>
+        <v>518046</v>
       </c>
       <c r="R8" t="n">
-        <v>6982404</v>
+        <v>6982481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986855</v>
+        <v>128986870</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518133</v>
+        <v>517964</v>
       </c>
       <c r="R11" t="n">
-        <v>6982572</v>
+        <v>6982433</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,6 +1647,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986870</v>
+        <v>128986855</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1689,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517964</v>
+        <v>518133</v>
       </c>
       <c r="R12" t="n">
-        <v>6982433</v>
+        <v>6982572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,11 +1749,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -865,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986869</v>
+        <v>128986854</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,21 +876,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517784</v>
+        <v>518021</v>
       </c>
       <c r="R4" t="n">
-        <v>6982724</v>
+        <v>6982497</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -936,11 +936,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986854</v>
+        <v>128986869</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -978,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518021</v>
+        <v>517784</v>
       </c>
       <c r="R5" t="n">
-        <v>6982497</v>
+        <v>6982724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,6 +1033,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -1067,7 +1067,7 @@
         <v>128986856</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>128986858</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>128986857</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>128986859</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986861</v>
+        <v>128986873</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517866</v>
+        <v>517923</v>
       </c>
       <c r="R2" t="n">
-        <v>6982544</v>
+        <v>6982402</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986868</v>
+        <v>128986861</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,19 +783,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517857</v>
+        <v>517866</v>
       </c>
       <c r="R3" t="n">
-        <v>6982472</v>
+        <v>6982544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986854</v>
+        <v>128986862</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -900,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518021</v>
+        <v>517897</v>
       </c>
       <c r="R4" t="n">
-        <v>6982497</v>
+        <v>6982478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986869</v>
+        <v>128986863</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517784</v>
+        <v>518023</v>
       </c>
       <c r="R5" t="n">
-        <v>6982724</v>
+        <v>6982495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1033,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986856</v>
+        <v>128986874</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>92605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517896</v>
+        <v>517913</v>
       </c>
       <c r="R6" t="n">
-        <v>6982517</v>
+        <v>6982711</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1135,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986871</v>
+        <v>128986854</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517990</v>
+        <v>518021</v>
       </c>
       <c r="R7" t="n">
-        <v>6982404</v>
+        <v>6982497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986858</v>
+        <v>128986855</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,46 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518046</v>
+        <v>518133</v>
       </c>
       <c r="R8" t="n">
-        <v>6982481</v>
+        <v>6982572</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986862</v>
+        <v>128986869</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517897</v>
+        <v>517784</v>
       </c>
       <c r="R9" t="n">
-        <v>6982478</v>
+        <v>6982724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1453,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986860</v>
+        <v>128986870</v>
       </c>
       <c r="B10" t="n">
-        <v>79130</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1514,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517810</v>
+        <v>517964</v>
       </c>
       <c r="R10" t="n">
-        <v>6982735</v>
+        <v>6982433</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1550,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1576,14 +1558,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986870</v>
+        <v>128986871</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1611,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517964</v>
+        <v>517990</v>
       </c>
       <c r="R11" t="n">
-        <v>6982433</v>
+        <v>6982404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986855</v>
+        <v>128986860</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>79413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1689,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6450</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1713,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518133</v>
+        <v>517810</v>
       </c>
       <c r="R12" t="n">
-        <v>6982572</v>
+        <v>6982735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986867</v>
+        <v>128986864</v>
       </c>
       <c r="B13" t="n">
-        <v>56908</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1786,42 +1768,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517871</v>
+        <v>517901</v>
       </c>
       <c r="R13" t="n">
-        <v>6982707</v>
+        <v>6982724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128986857</v>
+        <v>128986865</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1891,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1915,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517910</v>
+        <v>517835</v>
       </c>
       <c r="R14" t="n">
-        <v>6982520</v>
+        <v>6982835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,11 +1925,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1982,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986874</v>
+        <v>128986866</v>
       </c>
       <c r="B15" t="n">
-        <v>92241</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2017,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>517913</v>
+        <v>517804</v>
       </c>
       <c r="R15" t="n">
-        <v>6982711</v>
+        <v>6982850</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986873</v>
+        <v>128986856</v>
       </c>
       <c r="B16" t="n">
-        <v>88950</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2090,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>517923</v>
+        <v>517896</v>
       </c>
       <c r="R16" t="n">
-        <v>6982402</v>
+        <v>6982517</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2176,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986859</v>
+        <v>128986857</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2211,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>517919</v>
+        <v>517910</v>
       </c>
       <c r="R17" t="n">
-        <v>6982719</v>
+        <v>6982520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986863</v>
+        <v>128986858</v>
       </c>
       <c r="B18" t="n">
-        <v>91848</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2289,34 +2263,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518023</v>
+        <v>518046</v>
       </c>
       <c r="R18" t="n">
-        <v>6982495</v>
+        <v>6982481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,6 +2335,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2375,10 +2366,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986865</v>
+        <v>128986859</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2386,21 +2377,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2410,10 +2401,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>517835</v>
+        <v>517919</v>
       </c>
       <c r="R19" t="n">
-        <v>6982835</v>
+        <v>6982719</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,6 +2437,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2472,45 +2468,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986864</v>
+        <v>128986867</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>57132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kvarndalen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>517901</v>
+        <v>517871</v>
       </c>
       <c r="R20" t="n">
-        <v>6982724</v>
+        <v>6982707</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 28289-2025 artfynd.xlsx
+++ b/artfynd/A 28289-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986861</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986862</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986863</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986874</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986854</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986869</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986871</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986860</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986864</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986865</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986866</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986856</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2249,6 +2329,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986857</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2363,6 +2448,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986858</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2465,6 +2555,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986859</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2570,8 +2665,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128986867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>